--- a/青海24示范小流域-药草沟-20260313/630121_大通/成果报表/附表3_沟滩占地情况调查成果表.xlsx
+++ b/青海24示范小流域-药草沟-20260313/630121_大通/成果报表/附表3_沟滩占地情况调查成果表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenh\Desktop\青海24示范小流域-药草沟-202603\630121_大通\成果报表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\空间数据检查桌面版-主题-design-2026\青海24示范小流域-药草沟-20260313\630121_大通\成果报表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43372D44-9462-45EF-903F-B0662DD4E0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C74557D-4104-4C6F-8DAD-2F279CB24C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1800" windowWidth="22905" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="1455" windowWidth="24945" windowHeight="14295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="沟滩占地情况调查成果表" sheetId="1" r:id="rId1"/>
@@ -355,46 +355,6 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">14. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-      </rPr>
-      <t>河流名称</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">15. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-      </rPr>
-      <t>河流代码</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
       <t>16.</t>
     </r>
     <r>
@@ -469,6 +429,36 @@
   </si>
   <si>
     <t>101.656807</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>14.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="FangSong"/>
+        <family val="3"/>
+      </rPr>
+      <t>河流名称</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>15.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="FangSong"/>
+        <family val="3"/>
+      </rPr>
+      <t>河流代码</t>
+    </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1222,13 +1212,13 @@
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="15" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="19.149999999999999" customHeight="1" thickBot="1">
@@ -1236,31 +1226,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="17">
         <v>630121</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" s="17">
         <v>630121102</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I2" s="20">
         <v>37.065978000000001</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K2" s="12">
         <v>7.8</v>
@@ -1269,16 +1259,16 @@
         <v>2.8</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N2" s="11">
         <v>58</v>
       </c>
       <c r="O2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>25</v>
       </c>
       <c r="Q2" s="6"/>
     </row>
@@ -1287,31 +1277,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="17">
         <v>630121</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" s="17">
         <v>630121102</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I3" s="20">
         <v>37.046616999999998</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K3" s="13">
         <v>8.01</v>
@@ -1320,16 +1310,16 @@
         <v>2.36</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N3" s="14">
         <v>29</v>
       </c>
       <c r="O3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>25</v>
       </c>
       <c r="Q3" s="6"/>
     </row>
